--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487684_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487684_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2102</v>
+        <v>6.4377</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4316</v>
+        <v>5.6318</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7786</v>
+        <v>0.8058</v>
       </c>
       <c r="G2" t="n">
         <v>3.9167</v>
@@ -610,13 +610,13 @@
         <v>2.3284</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9767</v>
+        <v>-0.7492</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4599</v>
+        <v>-0.2597</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5168</v>
+        <v>-0.4895</v>
       </c>
       <c r="V2" t="n">
         <v>0.9418</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9564</v>
+        <v>4.9287</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6571</v>
+        <v>3.3568</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2993</v>
+        <v>1.5719</v>
       </c>
       <c r="G3" t="n">
         <v>2.713</v>
@@ -688,13 +688,13 @@
         <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4374</v>
+        <v>0.4096</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7896</v>
+        <v>0.4893</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3522</v>
+        <v>-0.0796</v>
       </c>
       <c r="V3" t="n">
         <v>1.2239</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9274</v>
+        <v>3.7768</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0753</v>
+        <v>3.6738</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8521</v>
+        <v>0.103</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4156</v>
+        <v>2.7715</v>
       </c>
       <c r="H4" t="n">
-        <v>2.479</v>
+        <v>0.2834</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0634</v>
+        <v>2.4881</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8319</v>
+        <v>3.1793</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7507</v>
+        <v>0.5355</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08119999999999999</v>
+        <v>2.6438</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5837</v>
+        <v>-0.4079</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7282999999999999</v>
+        <v>-0.2521</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1446</v>
+        <v>-0.1557</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7463</v>
+        <v>1.3582</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7463</v>
+        <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6117</v>
+        <v>-0.9648</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2434</v>
+        <v>-0.1175</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3684</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8462</v>
+        <v>0.6119</v>
       </c>
       <c r="W4" t="n">
+        <v>0.6119</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.8462</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4254</v>
+        <v>3.2728</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5131</v>
+        <v>1.775</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0877</v>
+        <v>1.4978</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7715</v>
+        <v>2.4156</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2834</v>
+        <v>2.479</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4881</v>
+        <v>-0.0634</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1793</v>
+        <v>1.8319</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5355</v>
+        <v>1.7507</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6438</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4079</v>
+        <v>0.5837</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2521</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1557</v>
+        <v>-0.1446</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3582</v>
+        <v>1.7463</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3582</v>
+        <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3163</v>
+        <v>-0.0429</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2782</v>
+        <v>-0.0569</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0381</v>
+        <v>0.014</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6119</v>
+        <v>-0.8462</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1576</v>
+        <v>2.7032</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8085</v>
+        <v>3.7084</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6508</v>
+        <v>-1.0052</v>
       </c>
       <c r="G6" t="n">
         <v>6.6132</v>
@@ -922,13 +922,13 @@
         <v>2.1344</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3325</v>
+        <v>-0.122</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0258</v>
+        <v>-0.0743</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3067</v>
+        <v>-0.0476</v>
       </c>
       <c r="V6" t="n">
         <v>-3.0119</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3318</v>
+        <v>2.6138</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6978</v>
+        <v>0.898</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6341</v>
+        <v>1.7159</v>
       </c>
       <c r="G7" t="n">
         <v>4.0515</v>
@@ -1000,13 +1000,13 @@
         <v>2.5224</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2555</v>
+        <v>-0.9735</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.4414</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6139</v>
+        <v>-0.5322</v>
       </c>
       <c r="V7" t="n">
         <v>0.894</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1556</v>
+        <v>-0.659</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0575</v>
+        <v>-0.2823</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2131</v>
+        <v>-0.3766</v>
       </c>
       <c r="G8" t="n">
         <v>3.3339</v>
@@ -1078,13 +1078,13 @@
         <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2851</v>
+        <v>0.7817</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9836</v>
+        <v>0.6438</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3015</v>
+        <v>0.138</v>
       </c>
       <c r="V8" t="n">
         <v>-0.894</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4991</v>
+        <v>-1.0203</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9178</v>
+        <v>-1.6571</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4187</v>
+        <v>0.6368</v>
       </c>
       <c r="G9" t="n">
         <v>1.16</v>
@@ -1156,13 +1156,13 @@
         <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0487</v>
+        <v>0.4301</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3039</v>
+        <v>0.5647</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3526</v>
+        <v>-0.1346</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2821</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.125</v>
+        <v>-1.5249</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8723</v>
+        <v>-1.572</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2527</v>
+        <v>0.0472</v>
       </c>
       <c r="G10" t="n">
         <v>0.3178</v>
@@ -1234,13 +1234,13 @@
         <v>0.3881</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6368</v>
+        <v>-0.0367</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3028</v>
+        <v>-0.0025</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.334</v>
+        <v>-0.0342</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2239</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. GUEYE</t>
+          <t>E. LLACER SIMLAT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2052</v>
+        <v>-2.8618</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2116</v>
+        <v>-1.5728</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9936</v>
+        <v>-1.289</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4425</v>
+        <v>-1.3376</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7441</v>
+        <v>-0.8099</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1867</v>
+        <v>-0.5278</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1654</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9238</v>
+        <v>-0.5808</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.7584</v>
+        <v>0.0228</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6079</v>
+        <v>-0.7796</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1796</v>
+        <v>-0.229</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4282</v>
+        <v>-0.5506</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3881</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5209</v>
+        <v>0.0878</v>
       </c>
       <c r="T11" t="n">
-        <v>0.923</v>
+        <v>-0.0446</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4022</v>
+        <v>0.1324</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.6716</v>
+        <v>-1.2239</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.3418</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. LLACER SIMLAT</t>
+          <t>S. GUEYE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4228</v>
+        <v>-3.7631</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1338</v>
+        <v>-0.5515</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.289</v>
+        <v>-3.2116</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.3376</v>
+        <v>-0.4425</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8099</v>
+        <v>1.7441</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5278</v>
+        <v>-2.1867</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5580000000000001</v>
+        <v>0.1654</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5808</v>
+        <v>1.9238</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0228</v>
+        <v>-1.7584</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7796</v>
+        <v>-0.6079</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.229</v>
+        <v>-0.1796</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5506</v>
+        <v>-0.4282</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3881</v>
+        <v>0.3881</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4733</v>
+        <v>-0.037</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6057</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1324</v>
+        <v>-0.6202</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2239</v>
+        <v>-3.6716</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2239</v>
+        <v>-3.3418</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.6011</v>
+        <v>13.9039</v>
       </c>
       <c r="E13" t="n">
-        <v>13.1054</v>
+        <v>13.4081</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4959000000000005</v>
+        <v>0.4960000000000004</v>
       </c>
       <c r="G13" t="n">
         <v>25.5131</v>
@@ -1438,7 +1438,7 @@
         <v>18.1167</v>
       </c>
       <c r="I13" t="n">
-        <v>7.396300000000001</v>
+        <v>7.396300000000002</v>
       </c>
       <c r="J13" t="n">
         <v>26.4168</v>
@@ -1468,10 +1468,10 @@
         <v>15.5227</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5197</v>
+        <v>-1.2169</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9811000000000002</v>
+        <v>1.2841</v>
       </c>
       <c r="U13" t="n">
         <v>-2.5008</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ GARCIA</t>
+          <t>M. RODRÍGUEZ RIVEROL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6066</v>
+        <v>1.7598</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7843</v>
+        <v>1.3412</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1777</v>
+        <v>0.4186</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1153</v>
+        <v>-0.2984</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.0467</v>
+        <v>-0.2406</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9314</v>
+        <v>-0.0578</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1881</v>
+        <v>0.4437</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0165</v>
+        <v>1.0298</v>
       </c>
       <c r="L14" t="n">
-        <v>3.1716</v>
+        <v>-0.5861</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.3034</v>
+        <v>-0.7421</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.0632</v>
+        <v>-1.2704</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2402</v>
+        <v>0.5283</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3582</v>
+        <v>2.1344</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1642</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5224</v>
+        <v>2.1344</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1397</v>
+        <v>-0.6881</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1962</v>
+        <v>-0.3264</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0565</v>
+        <v>-0.3617</v>
       </c>
       <c r="V14" t="n">
+        <v>0.6119</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.2239</v>
       </c>
-      <c r="W14" t="n">
-        <v>0.5642</v>
-      </c>
       <c r="X14" t="n">
-        <v>0.6597</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. RODRÍGUEZ RIVEROL</t>
+          <t>D. RODRIGUEZ GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2776</v>
+        <v>1.6827</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9408</v>
+        <v>2.7843</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3368</v>
+        <v>-1.1016</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2984</v>
+        <v>-1.1153</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2406</v>
+        <v>-3.0467</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0578</v>
+        <v>1.9314</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4437</v>
+        <v>3.1881</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0298</v>
+        <v>0.0165</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5861</v>
+        <v>3.1716</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7421</v>
+        <v>-4.3034</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2704</v>
+        <v>-3.0632</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5283</v>
+        <v>-1.2402</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1344</v>
+        <v>1.3582</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1642</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1344</v>
+        <v>2.5224</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1702</v>
+        <v>0.2159</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7268</v>
+        <v>0.1962</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4435</v>
+        <v>0.0197</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6119</v>
+        <v>1.2239</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2239</v>
+        <v>0.5642</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6119</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1516</v>
       </c>
       <c r="E16" t="n">
         <v>-0.0599</v>
       </c>
       <c r="F16" t="n">
-        <v>0.157</v>
+        <v>0.2115</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0838</v>
@@ -1702,13 +1702,13 @@
         <v>0.3881</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0848</v>
+        <v>-0.0303</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1211</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1224</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0589</v>
+        <v>0.1195</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5294</v>
+        <v>0.4293</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4705</v>
+        <v>-0.3097</v>
       </c>
       <c r="G17" t="n">
         <v>-1.8987</v>
@@ -1780,13 +1780,13 @@
         <v>0.5821</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3457</v>
+        <v>0.4063</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0617</v>
+        <v>-0.0384</v>
       </c>
       <c r="U17" t="n">
-        <v>0.284</v>
+        <v>0.4447</v>
       </c>
       <c r="V17" t="n">
         <v>1.2239</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4321</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1311</v>
+        <v>1.7307</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5632</v>
+        <v>-2.457</v>
       </c>
       <c r="G18" t="n">
         <v>-1.9083</v>
@@ -1858,13 +1858,13 @@
         <v>2.5224</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9284</v>
+        <v>0.6342</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0453</v>
+        <v>0.6449</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1168</v>
+        <v>-0.0106</v>
       </c>
       <c r="V18" t="n">
         <v>0.1597</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6997</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="E19" t="n">
         <v>-0.8646</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1649</v>
+        <v>-0.1349</v>
       </c>
       <c r="G19" t="n">
         <v>-2.4806</v>
@@ -1936,13 +1936,13 @@
         <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5393</v>
+        <v>0.2395</v>
       </c>
       <c r="T19" t="n">
         <v>0.0617</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4776</v>
+        <v>0.1778</v>
       </c>
       <c r="V19" t="n">
         <v>2.794</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9391</v>
+        <v>-1.3935</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2454</v>
+        <v>0.0549</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6936</v>
+        <v>-1.4484</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4474</v>
@@ -2014,13 +2014,13 @@
         <v>2.3284</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3692</v>
+        <v>0.1764</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0011</v>
+        <v>0.3014</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3703</v>
+        <v>-0.125</v>
       </c>
       <c r="V20" t="n">
         <v>0.4895</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. GARCÍA PEREZ</t>
+          <t>A. APARICIO IZQUIERDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8232</v>
+        <v>-2.6009</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0608</v>
+        <v>0.8469</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7624</v>
+        <v>-3.4479</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3679</v>
+        <v>-5.3019</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2694</v>
+        <v>-3.2304</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0984</v>
+        <v>-2.0715</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0612</v>
+        <v>-0.8997000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0206</v>
+        <v>-0.8692</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0406</v>
+        <v>-0.0305</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.429</v>
+        <v>-4.4022</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.29</v>
+        <v>-2.3612</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.139</v>
+        <v>-2.041</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6792</v>
+        <v>1.1771</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1817</v>
+        <v>0.881</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4975</v>
+        <v>0.2961</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6119</v>
+        <v>0.9418</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.8358</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6119</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. APARICIO IZQUIERDO</t>
+          <t>E. GARCÍA PEREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9045</v>
+        <v>-2.6686</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6467000000000001</v>
+        <v>-1.9607</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5513</v>
+        <v>-0.7079</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.3019</v>
+        <v>-0.3679</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.2304</v>
+        <v>-0.2694</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0715</v>
+        <v>-0.0984</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8997000000000001</v>
+        <v>0.0612</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8692</v>
+        <v>0.0206</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0305</v>
+        <v>0.0406</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.4022</v>
+        <v>-0.429</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.3612</v>
+        <v>-0.29</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.041</v>
+        <v>-0.139</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5821</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8735000000000001</v>
+        <v>-0.5246</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6808</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1927</v>
+        <v>-0.443</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9418</v>
+        <v>-0.6119</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8358</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.894</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8288</v>
+        <v>-3.4166</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3595</v>
+        <v>-2.4596</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4693</v>
+        <v>-0.957</v>
       </c>
       <c r="G23" t="n">
         <v>-4.6378</v>
@@ -2248,13 +2248,13 @@
         <v>3.2985</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2016</v>
+        <v>0.6138</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.0286</v>
       </c>
       <c r="V23" t="n">
         <v>1.3836</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0139</v>
+        <v>-4.1746</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9378</v>
+        <v>-2.3382</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0761</v>
+        <v>-1.8364</v>
       </c>
       <c r="G24" t="n">
         <v>-4.9731</v>
@@ -2326,13 +2326,13 @@
         <v>0.9702</v>
       </c>
       <c r="S24" t="n">
-        <v>0.795</v>
+        <v>0.6342</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7413</v>
+        <v>0.3409</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0536</v>
+        <v>0.2933</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6119</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-13.6011</v>
+        <v>-12.2664</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4957000000000005</v>
+        <v>-0.4957000000000007</v>
       </c>
       <c r="F25" t="n">
-        <v>-13.1054</v>
+        <v>-11.7707</v>
       </c>
       <c r="G25" t="n">
         <v>-25.5132</v>
@@ -2377,7 +2377,7 @@
         <v>-7.396199999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9036999999999993</v>
+        <v>0.9037000000000002</v>
       </c>
       <c r="K25" t="n">
         <v>0.04130000000000011</v>
@@ -2392,7 +2392,7 @@
         <v>-18.1583</v>
       </c>
       <c r="O25" t="n">
-        <v>-8.258599999999998</v>
+        <v>-8.258600000000001</v>
       </c>
       <c r="P25" t="n">
         <v>2.9106</v>
@@ -2404,13 +2404,13 @@
         <v>18.4331</v>
       </c>
       <c r="S25" t="n">
-        <v>1.5198</v>
+        <v>2.8544</v>
       </c>
       <c r="T25" t="n">
         <v>2.5009</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9812000000000002</v>
+        <v>0.3534999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>7.482099999999999</v>
